--- a/Valuation Framework.xlsx
+++ b/Valuation Framework.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C3AC4C9-C202-430F-81B0-3869E2C2087E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5FD1145-83FC-495A-A61D-25686AA7AF20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" activeTab="4" xr2:uid="{E998409C-6030-4F13-BFA3-5FA46D863087}"/>
+    <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" activeTab="2" xr2:uid="{E998409C-6030-4F13-BFA3-5FA46D863087}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="4" r:id="rId1"/>
@@ -1135,6 +1135,11 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="16" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1150,11 +1155,6 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="2" fontId="16" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -32379,7 +32379,7 @@
       <c r="D4" s="3"/>
       <c r="E4" s="32">
         <f ca="1">+TODAY()</f>
-        <v>45901</v>
+        <v>45922</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3" t="s">
@@ -35296,43 +35296,43 @@
       <c r="L53" s="3"/>
       <c r="M53" s="3">
         <f ca="1">YEARFRAC(E4,E5)</f>
-        <v>125.66944444444445</v>
+        <v>125.72777777777777</v>
       </c>
       <c r="N53" s="3">
         <f ca="1">M53+1</f>
-        <v>126.66944444444445</v>
+        <v>126.72777777777777</v>
       </c>
       <c r="O53" s="3">
         <f ca="1">N53+1</f>
-        <v>127.66944444444445</v>
+        <v>127.72777777777777</v>
       </c>
       <c r="P53" s="3">
         <f t="shared" ref="P53:V53" ca="1" si="16">O53+1</f>
-        <v>128.66944444444445</v>
+        <v>128.72777777777776</v>
       </c>
       <c r="Q53" s="3">
         <f t="shared" ca="1" si="16"/>
-        <v>129.66944444444445</v>
+        <v>129.72777777777776</v>
       </c>
       <c r="R53" s="3">
         <f t="shared" ca="1" si="16"/>
-        <v>130.66944444444445</v>
+        <v>130.72777777777776</v>
       </c>
       <c r="S53" s="3">
         <f t="shared" ca="1" si="16"/>
-        <v>131.66944444444445</v>
+        <v>131.72777777777776</v>
       </c>
       <c r="T53" s="3">
         <f t="shared" ca="1" si="16"/>
-        <v>132.66944444444445</v>
+        <v>132.72777777777776</v>
       </c>
       <c r="U53" s="3">
         <f t="shared" ca="1" si="16"/>
-        <v>133.66944444444445</v>
+        <v>133.72777777777776</v>
       </c>
       <c r="V53" s="3">
         <f t="shared" ca="1" si="16"/>
-        <v>134.66944444444445</v>
+        <v>134.72777777777776</v>
       </c>
       <c r="W53" s="3"/>
       <c r="X53" s="3"/>
@@ -36031,29 +36031,29 @@
     <row r="68" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A68" s="3"/>
       <c r="B68" s="66"/>
-      <c r="C68" s="67" t="s">
+      <c r="C68" s="72" t="s">
         <v>51</v>
       </c>
-      <c r="D68" s="67"/>
-      <c r="E68" s="67"/>
-      <c r="F68" s="67"/>
-      <c r="G68" s="67"/>
-      <c r="H68" s="67"/>
-      <c r="I68" s="67"/>
-      <c r="J68" s="68"/>
+      <c r="D68" s="72"/>
+      <c r="E68" s="72"/>
+      <c r="F68" s="72"/>
+      <c r="G68" s="72"/>
+      <c r="H68" s="72"/>
+      <c r="I68" s="72"/>
+      <c r="J68" s="73"/>
       <c r="K68" s="3"/>
       <c r="L68" s="3"/>
       <c r="M68" s="66"/>
-      <c r="N68" s="69" t="s">
+      <c r="N68" s="74" t="s">
         <v>201</v>
       </c>
-      <c r="O68" s="69"/>
-      <c r="P68" s="69"/>
-      <c r="Q68" s="69"/>
-      <c r="R68" s="69"/>
-      <c r="S68" s="69"/>
-      <c r="T68" s="69"/>
-      <c r="U68" s="70"/>
+      <c r="O68" s="74"/>
+      <c r="P68" s="74"/>
+      <c r="Q68" s="74"/>
+      <c r="R68" s="74"/>
+      <c r="S68" s="74"/>
+      <c r="T68" s="74"/>
+      <c r="U68" s="75"/>
       <c r="V68" s="3"/>
       <c r="W68" s="3"/>
       <c r="X68" s="3"/>
@@ -36079,36 +36079,36 @@
     </row>
     <row r="69" spans="1:43" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3"/>
-      <c r="B69" s="71" t="s">
+      <c r="B69" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="C69" s="72" t="e">
+      <c r="C69" s="67" t="e">
         <f ca="1">+J4</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D69" s="73"/>
-      <c r="E69" s="73"/>
-      <c r="F69" s="73"/>
-      <c r="G69" s="73"/>
-      <c r="H69" s="73"/>
-      <c r="I69" s="73"/>
-      <c r="J69" s="73"/>
+      <c r="D69" s="68"/>
+      <c r="E69" s="68"/>
+      <c r="F69" s="68"/>
+      <c r="G69" s="68"/>
+      <c r="H69" s="68"/>
+      <c r="I69" s="68"/>
+      <c r="J69" s="68"/>
       <c r="K69" s="3"/>
       <c r="L69" s="3"/>
-      <c r="M69" s="71" t="s">
+      <c r="M69" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="N69" s="72" t="e">
+      <c r="N69" s="67" t="e">
         <f ca="1">+J4</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="O69" s="73"/>
-      <c r="P69" s="73"/>
-      <c r="Q69" s="73"/>
-      <c r="R69" s="73"/>
-      <c r="S69" s="73"/>
-      <c r="T69" s="73"/>
-      <c r="U69" s="73"/>
+      <c r="O69" s="68"/>
+      <c r="P69" s="68"/>
+      <c r="Q69" s="68"/>
+      <c r="R69" s="68"/>
+      <c r="S69" s="68"/>
+      <c r="T69" s="68"/>
+      <c r="U69" s="68"/>
       <c r="V69" s="3"/>
       <c r="W69" s="3"/>
       <c r="X69" s="3"/>
@@ -36134,26 +36134,26 @@
     </row>
     <row r="70" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A70" s="3"/>
-      <c r="B70" s="71"/>
-      <c r="C70" s="74"/>
-      <c r="D70" s="75"/>
-      <c r="E70" s="75"/>
-      <c r="F70" s="75"/>
-      <c r="G70" s="76"/>
-      <c r="H70" s="75"/>
-      <c r="I70" s="75"/>
-      <c r="J70" s="75"/>
+      <c r="B70" s="76"/>
+      <c r="C70" s="69"/>
+      <c r="D70" s="70"/>
+      <c r="E70" s="70"/>
+      <c r="F70" s="70"/>
+      <c r="G70" s="71"/>
+      <c r="H70" s="70"/>
+      <c r="I70" s="70"/>
+      <c r="J70" s="70"/>
       <c r="K70" s="3"/>
       <c r="L70" s="3"/>
-      <c r="M70" s="71"/>
-      <c r="N70" s="74"/>
-      <c r="O70" s="75"/>
-      <c r="P70" s="75"/>
-      <c r="Q70" s="75"/>
-      <c r="R70" s="76"/>
-      <c r="S70" s="75"/>
-      <c r="T70" s="75"/>
-      <c r="U70" s="75"/>
+      <c r="M70" s="76"/>
+      <c r="N70" s="69"/>
+      <c r="O70" s="70"/>
+      <c r="P70" s="70"/>
+      <c r="Q70" s="70"/>
+      <c r="R70" s="71"/>
+      <c r="S70" s="70"/>
+      <c r="T70" s="70"/>
+      <c r="U70" s="70"/>
       <c r="V70" s="3"/>
       <c r="W70" s="3"/>
       <c r="X70" s="3"/>
@@ -36179,26 +36179,26 @@
     </row>
     <row r="71" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A71" s="3"/>
-      <c r="B71" s="71"/>
-      <c r="C71" s="74"/>
-      <c r="D71" s="75"/>
-      <c r="E71" s="75"/>
-      <c r="F71" s="75"/>
-      <c r="G71" s="76"/>
-      <c r="H71" s="75"/>
-      <c r="I71" s="75"/>
-      <c r="J71" s="75"/>
+      <c r="B71" s="76"/>
+      <c r="C71" s="69"/>
+      <c r="D71" s="70"/>
+      <c r="E71" s="70"/>
+      <c r="F71" s="70"/>
+      <c r="G71" s="71"/>
+      <c r="H71" s="70"/>
+      <c r="I71" s="70"/>
+      <c r="J71" s="70"/>
       <c r="K71" s="3"/>
       <c r="L71" s="3"/>
-      <c r="M71" s="71"/>
-      <c r="N71" s="74"/>
-      <c r="O71" s="75"/>
-      <c r="P71" s="75"/>
-      <c r="Q71" s="75"/>
-      <c r="R71" s="76"/>
-      <c r="S71" s="75"/>
-      <c r="T71" s="75"/>
-      <c r="U71" s="75"/>
+      <c r="M71" s="76"/>
+      <c r="N71" s="69"/>
+      <c r="O71" s="70"/>
+      <c r="P71" s="70"/>
+      <c r="Q71" s="70"/>
+      <c r="R71" s="71"/>
+      <c r="S71" s="70"/>
+      <c r="T71" s="70"/>
+      <c r="U71" s="70"/>
       <c r="V71" s="3"/>
       <c r="W71" s="3"/>
       <c r="X71" s="3"/>
@@ -36224,26 +36224,26 @@
     </row>
     <row r="72" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A72" s="3"/>
-      <c r="B72" s="71"/>
-      <c r="C72" s="74"/>
-      <c r="D72" s="76"/>
-      <c r="E72" s="76"/>
-      <c r="F72" s="76"/>
-      <c r="G72" s="76"/>
-      <c r="H72" s="76"/>
-      <c r="I72" s="76"/>
-      <c r="J72" s="76"/>
+      <c r="B72" s="76"/>
+      <c r="C72" s="69"/>
+      <c r="D72" s="71"/>
+      <c r="E72" s="71"/>
+      <c r="F72" s="71"/>
+      <c r="G72" s="71"/>
+      <c r="H72" s="71"/>
+      <c r="I72" s="71"/>
+      <c r="J72" s="71"/>
       <c r="K72" s="3"/>
       <c r="L72" s="3"/>
-      <c r="M72" s="71"/>
-      <c r="N72" s="74"/>
-      <c r="O72" s="76"/>
-      <c r="P72" s="76"/>
-      <c r="Q72" s="76"/>
-      <c r="R72" s="76"/>
-      <c r="S72" s="76"/>
-      <c r="T72" s="76"/>
-      <c r="U72" s="76"/>
+      <c r="M72" s="76"/>
+      <c r="N72" s="69"/>
+      <c r="O72" s="71"/>
+      <c r="P72" s="71"/>
+      <c r="Q72" s="71"/>
+      <c r="R72" s="71"/>
+      <c r="S72" s="71"/>
+      <c r="T72" s="71"/>
+      <c r="U72" s="71"/>
       <c r="V72" s="3"/>
       <c r="W72" s="3"/>
       <c r="X72" s="3"/>
@@ -36269,26 +36269,26 @@
     </row>
     <row r="73" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A73" s="3"/>
-      <c r="B73" s="71"/>
-      <c r="C73" s="74"/>
-      <c r="D73" s="75"/>
-      <c r="E73" s="75"/>
-      <c r="F73" s="75"/>
-      <c r="G73" s="76"/>
-      <c r="H73" s="75"/>
-      <c r="I73" s="75"/>
-      <c r="J73" s="75"/>
+      <c r="B73" s="76"/>
+      <c r="C73" s="69"/>
+      <c r="D73" s="70"/>
+      <c r="E73" s="70"/>
+      <c r="F73" s="70"/>
+      <c r="G73" s="71"/>
+      <c r="H73" s="70"/>
+      <c r="I73" s="70"/>
+      <c r="J73" s="70"/>
       <c r="K73" s="3"/>
       <c r="L73" s="3"/>
-      <c r="M73" s="71"/>
-      <c r="N73" s="74"/>
-      <c r="O73" s="75"/>
-      <c r="P73" s="75"/>
-      <c r="Q73" s="75"/>
-      <c r="R73" s="76"/>
-      <c r="S73" s="75"/>
-      <c r="T73" s="75"/>
-      <c r="U73" s="75"/>
+      <c r="M73" s="76"/>
+      <c r="N73" s="69"/>
+      <c r="O73" s="70"/>
+      <c r="P73" s="70"/>
+      <c r="Q73" s="70"/>
+      <c r="R73" s="71"/>
+      <c r="S73" s="70"/>
+      <c r="T73" s="70"/>
+      <c r="U73" s="70"/>
       <c r="V73" s="3"/>
       <c r="W73" s="3"/>
       <c r="X73" s="3"/>
@@ -36314,26 +36314,26 @@
     </row>
     <row r="74" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A74" s="3"/>
-      <c r="B74" s="71"/>
-      <c r="C74" s="74"/>
-      <c r="D74" s="75"/>
-      <c r="E74" s="75"/>
-      <c r="F74" s="75"/>
-      <c r="G74" s="76"/>
-      <c r="H74" s="75"/>
-      <c r="I74" s="75"/>
-      <c r="J74" s="75"/>
+      <c r="B74" s="76"/>
+      <c r="C74" s="69"/>
+      <c r="D74" s="70"/>
+      <c r="E74" s="70"/>
+      <c r="F74" s="70"/>
+      <c r="G74" s="71"/>
+      <c r="H74" s="70"/>
+      <c r="I74" s="70"/>
+      <c r="J74" s="70"/>
       <c r="K74" s="3"/>
       <c r="L74" s="3"/>
-      <c r="M74" s="71"/>
-      <c r="N74" s="74"/>
-      <c r="O74" s="75"/>
-      <c r="P74" s="75"/>
-      <c r="Q74" s="75"/>
-      <c r="R74" s="76"/>
-      <c r="S74" s="75"/>
-      <c r="T74" s="75"/>
-      <c r="U74" s="75"/>
+      <c r="M74" s="76"/>
+      <c r="N74" s="69"/>
+      <c r="O74" s="70"/>
+      <c r="P74" s="70"/>
+      <c r="Q74" s="70"/>
+      <c r="R74" s="71"/>
+      <c r="S74" s="70"/>
+      <c r="T74" s="70"/>
+      <c r="U74" s="70"/>
       <c r="V74" s="3"/>
       <c r="W74" s="3"/>
       <c r="X74" s="3"/>
@@ -36359,26 +36359,26 @@
     </row>
     <row r="75" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A75" s="3"/>
-      <c r="B75" s="71"/>
-      <c r="C75" s="74"/>
-      <c r="D75" s="75"/>
-      <c r="E75" s="75"/>
-      <c r="F75" s="75"/>
-      <c r="G75" s="76"/>
-      <c r="H75" s="75"/>
-      <c r="I75" s="75"/>
-      <c r="J75" s="75"/>
+      <c r="B75" s="76"/>
+      <c r="C75" s="69"/>
+      <c r="D75" s="70"/>
+      <c r="E75" s="70"/>
+      <c r="F75" s="70"/>
+      <c r="G75" s="71"/>
+      <c r="H75" s="70"/>
+      <c r="I75" s="70"/>
+      <c r="J75" s="70"/>
       <c r="K75" s="3"/>
       <c r="L75" s="3"/>
-      <c r="M75" s="71"/>
-      <c r="N75" s="74"/>
-      <c r="O75" s="75"/>
-      <c r="P75" s="75"/>
-      <c r="Q75" s="75"/>
-      <c r="R75" s="76"/>
-      <c r="S75" s="75"/>
-      <c r="T75" s="75"/>
-      <c r="U75" s="75"/>
+      <c r="M75" s="76"/>
+      <c r="N75" s="69"/>
+      <c r="O75" s="70"/>
+      <c r="P75" s="70"/>
+      <c r="Q75" s="70"/>
+      <c r="R75" s="71"/>
+      <c r="S75" s="70"/>
+      <c r="T75" s="70"/>
+      <c r="U75" s="70"/>
       <c r="V75" s="3"/>
       <c r="W75" s="3"/>
       <c r="X75" s="3"/>
@@ -36405,25 +36405,25 @@
     <row r="76" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A76" s="3"/>
       <c r="B76" s="77"/>
-      <c r="C76" s="74"/>
-      <c r="D76" s="75"/>
-      <c r="E76" s="75"/>
-      <c r="F76" s="75"/>
-      <c r="G76" s="76"/>
-      <c r="H76" s="75"/>
-      <c r="I76" s="75"/>
-      <c r="J76" s="75"/>
+      <c r="C76" s="69"/>
+      <c r="D76" s="70"/>
+      <c r="E76" s="70"/>
+      <c r="F76" s="70"/>
+      <c r="G76" s="71"/>
+      <c r="H76" s="70"/>
+      <c r="I76" s="70"/>
+      <c r="J76" s="70"/>
       <c r="K76" s="3"/>
       <c r="L76" s="3"/>
       <c r="M76" s="77"/>
-      <c r="N76" s="74"/>
-      <c r="O76" s="75"/>
-      <c r="P76" s="75"/>
-      <c r="Q76" s="75"/>
-      <c r="R76" s="76"/>
-      <c r="S76" s="75"/>
-      <c r="T76" s="75"/>
-      <c r="U76" s="75"/>
+      <c r="N76" s="69"/>
+      <c r="O76" s="70"/>
+      <c r="P76" s="70"/>
+      <c r="Q76" s="70"/>
+      <c r="R76" s="71"/>
+      <c r="S76" s="70"/>
+      <c r="T76" s="70"/>
+      <c r="U76" s="70"/>
       <c r="V76" s="3"/>
       <c r="W76" s="3"/>
       <c r="X76" s="3"/>

--- a/Valuation Framework.xlsx
+++ b/Valuation Framework.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5FD1145-83FC-495A-A61D-25686AA7AF20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FB7999D-5A15-45DD-BFCA-350A19FFB584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" activeTab="2" xr2:uid="{E998409C-6030-4F13-BFA3-5FA46D863087}"/>
+    <workbookView xWindow="225" yWindow="3855" windowWidth="38175" windowHeight="15240" activeTab="2" xr2:uid="{E998409C-6030-4F13-BFA3-5FA46D863087}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="4" r:id="rId1"/>
@@ -32379,7 +32379,7 @@
       <c r="D4" s="3"/>
       <c r="E4" s="32">
         <f ca="1">+TODAY()</f>
-        <v>45922</v>
+        <v>46004</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3" t="s">
@@ -35296,43 +35296,43 @@
       <c r="L53" s="3"/>
       <c r="M53" s="3">
         <f ca="1">YEARFRAC(E4,E5)</f>
-        <v>125.72777777777777</v>
+        <v>125.95277777777778</v>
       </c>
       <c r="N53" s="3">
         <f ca="1">M53+1</f>
-        <v>126.72777777777777</v>
+        <v>126.95277777777778</v>
       </c>
       <c r="O53" s="3">
         <f ca="1">N53+1</f>
-        <v>127.72777777777777</v>
+        <v>127.95277777777778</v>
       </c>
       <c r="P53" s="3">
         <f t="shared" ref="P53:V53" ca="1" si="16">O53+1</f>
-        <v>128.72777777777776</v>
+        <v>128.95277777777778</v>
       </c>
       <c r="Q53" s="3">
         <f t="shared" ca="1" si="16"/>
-        <v>129.72777777777776</v>
+        <v>129.95277777777778</v>
       </c>
       <c r="R53" s="3">
         <f t="shared" ca="1" si="16"/>
-        <v>130.72777777777776</v>
+        <v>130.95277777777778</v>
       </c>
       <c r="S53" s="3">
         <f t="shared" ca="1" si="16"/>
-        <v>131.72777777777776</v>
+        <v>131.95277777777778</v>
       </c>
       <c r="T53" s="3">
         <f t="shared" ca="1" si="16"/>
-        <v>132.72777777777776</v>
+        <v>132.95277777777778</v>
       </c>
       <c r="U53" s="3">
         <f t="shared" ca="1" si="16"/>
-        <v>133.72777777777776</v>
+        <v>133.95277777777778</v>
       </c>
       <c r="V53" s="3">
         <f t="shared" ca="1" si="16"/>
-        <v>134.72777777777776</v>
+        <v>134.95277777777778</v>
       </c>
       <c r="W53" s="3"/>
       <c r="X53" s="3"/>
